--- a/public/nuvent-guest-list-template.xlsx
+++ b/public/nuvent-guest-list-template.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Guests" sheetId="1" r:id="rId1"/>
     <sheet name="Instructions" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
@@ -398,288 +398,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:C3"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
-    <col min="5" max="5" width="13.83203125" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" customWidth="1"/>
-    <col min="7" max="7" width="10.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-    <col min="13" max="13" width="13.83203125" customWidth="1"/>
-    <col min="14" max="14" width="13.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="10.83203125" customWidth="1"/>
-    <col min="18" max="18" width="10.83203125" customWidth="1"/>
-    <col min="19" max="19" width="13.83203125" customWidth="1"/>
-    <col min="20" max="20" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="28.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>U</v>
+        <v>Name</v>
       </c>
       <c r="B1" t="str">
-        <v>SR.NO</v>
+        <v>Contact</v>
       </c>
       <c r="C1" t="str">
-        <v/>
-      </c>
-      <c r="D1" t="str">
-        <v>PLACE</v>
-      </c>
-      <c r="E1" t="str">
-        <v>CONTACT</v>
-      </c>
-      <c r="F1" t="str">
-        <v>ID</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Romm</v>
-      </c>
-      <c r="H1" t="str">
-        <v>bed</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Pax</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Arrival Date</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Time</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Mode</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Details</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Pick up</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Remark</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Departure Date</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Time</v>
-      </c>
-      <c r="R1" t="str">
-        <v>Mode</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Details</v>
-      </c>
-      <c r="T1" t="str">
-        <v>Drop</v>
+        <v>City</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>RAMESH SHARMA</v>
+      </c>
+      <c r="B2" t="str">
+        <v>9876543210</v>
       </c>
       <c r="C2" t="str">
-        <v>RAMESH SHARMA</v>
-      </c>
-      <c r="D2" t="str">
         <v>SURAT</v>
-      </c>
-      <c r="E2">
-        <v>9876543210</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-      <c r="J2" t="str">
-        <v>22nd</v>
-      </c>
-      <c r="K2" t="str">
-        <v>10:30</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Train</v>
-      </c>
-      <c r="M2" t="str">
-        <v>19004 / KHANDESH EXP</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Surat Station</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Bride side</v>
-      </c>
-      <c r="P2" t="str">
-        <v>26th</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>18:00</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Train</v>
-      </c>
-      <c r="S2" t="str">
-        <v>19003 / KHANDESH EXP</v>
-      </c>
-      <c r="T2" t="str">
-        <v>Surat Station</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3">
-        <v>2</v>
+        <v>SUNITA PATEL</v>
+      </c>
+      <c r="B3" t="str">
+        <v>9123456780</v>
       </c>
       <c r="C3" t="str">
-        <v>SUNITA SHARMA</v>
-      </c>
-      <c r="D3" t="str">
-        <v>SURAT</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
-      <c r="O3" t="str">
-        <v/>
-      </c>
-      <c r="P3" t="str">
-        <v/>
-      </c>
-      <c r="Q3" t="str">
-        <v/>
-      </c>
-      <c r="R3" t="str">
-        <v/>
-      </c>
-      <c r="S3" t="str">
-        <v/>
-      </c>
-      <c r="T3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" t="str">
-        <v>MOHAN PATEL</v>
-      </c>
-      <c r="D4" t="str">
         <v>BARODA</v>
-      </c>
-      <c r="E4">
-        <v>9123456780</v>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4" t="str">
-        <v>23rd</v>
-      </c>
-      <c r="K4" t="str">
-        <v>14:00</v>
-      </c>
-      <c r="L4" t="str">
-        <v>By Road</v>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
-      <c r="N4" t="str">
-        <v>Hotel</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Groom side</v>
-      </c>
-      <c r="P4" t="str">
-        <v>25th</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>09:00</v>
-      </c>
-      <c r="R4" t="str">
-        <v>By Road</v>
-      </c>
-      <c r="S4" t="str">
-        <v/>
-      </c>
-      <c r="T4" t="str">
-        <v>Hotel</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A22"/>
   <cols>
     <col min="1" max="1" width="76.83203125" customWidth="1"/>
   </cols>
@@ -696,17 +464,17 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1. Do not rename, reorder or delete any column on the "Sheet1" tab.</v>
+        <v>One guest per row. That is the whole rule.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">   The third column header is INTENTIONALLY BLANK — that is the name</v>
+        <v/>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v xml:space="preserve">   column. Leaving it blank is correct; labelling it breaks the import.</v>
+        <v>1. "Name" — the person you will phone. Required.</v>
       </c>
     </row>
     <row r="6">
@@ -716,17 +484,17 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2. One family per U number. Put the number ONLY on the family's first</v>
+        <v>2. "Contact" — their phone number. 10 digits. Required.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">   row (the person you will phone). Every other member of that family</v>
+        <v xml:space="preserve">   +91, spaces and dashes are fine. A number stored by Excel as a</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">   leaves U BLANK and continues SR.NO: 1, 2, 3...</v>
+        <v xml:space="preserve">   decimal is handled.</v>
       </c>
     </row>
     <row r="10">
@@ -736,122 +504,67 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">   A row with a blank U and an SR.NO that does not continue the sequence</v>
+        <v>3. "City" — optional. It shows on the rooming list later.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">   is not imported. It is reported to you before anything is written —</v>
+        <v xml:space="preserve">   Any further columns to the RIGHT are ignored.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">   nothing is dropped silently — but it does have to be fixed.</v>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v>4. The tab can be called anything. Add as many guests as you like.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3. CONTACT goes on the family's first row. 10 digits. +91 and spaces are</v>
+        <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">   fine. A number stored by Excel as a decimal is handled.</v>
+        <v>NEED THE FULL FORMAT? The app already writes it for you. Export the guest</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v/>
+        <v>list from the app (Guest Master), edit it in Excel, and upload it straight</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>4. Pax is the TOTAL number of people in that family, including anyone</v>
+        <v>back — the importer reads the export as-is, travel legs and all.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">   whose name you have not listed. If Pax is 5 and you have named 2, the</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v xml:space="preserve">   import tells you so — that is a question for the phone call, not an</v>
+        <v>NOTHING IS WRITTEN UNTIL YOU PRESS COMMIT. The import screen shows a full</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v xml:space="preserve">   error.</v>
+        <v>preview first: how many guests, every warning, and every row it could not</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>5. Dates can be written as 22nd, 22, or 22/08/2026. They are resolved</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v xml:space="preserve">   against the event dates set in the app. A date outside those dates is</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v xml:space="preserve">   kept as raw text rather than guessed into the wrong day.</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>6. Times: 10:30 or 10.30 AM. Mode: Train / Flight / By Road / Bus.</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>7. Blank rows are ignored. Extra columns to the RIGHT are ignored.</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>NOTHING IS WRITTEN UNTIL YOU PRESS COMMIT. The import screen shows a full</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>preview first: how many families, how many guests, every warning, and</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>every row it could not place. Read that screen.</v>
+        <v>read. Read that screen.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A33"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A22"/>
   </ignoredErrors>
 </worksheet>
 </file>